--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20222.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="96">
   <si>
     <t>Mat</t>
   </si>
@@ -88,28 +88,148 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>ASCENCION</t>
+  </si>
+  <si>
+    <t>BALTAZARES</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>ELPIDIO</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
     <t>RICO</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MORENO</t>
   </si>
   <si>
     <t>NAJERA</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>TZIZIHUA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>VALIENTE</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>TZIZIHUA</t>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>QUIÑONES</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>REYLI</t>
+  </si>
+  <si>
+    <t>YARED</t>
+  </si>
+  <si>
+    <t>JOSE ISAAC</t>
+  </si>
+  <si>
+    <t>ALONDRA YURIDIA</t>
   </si>
   <si>
     <t>CRISTIAN FERMIN</t>
@@ -118,10 +238,73 @@
     <t>ALBERTO SHAKIB</t>
   </si>
   <si>
+    <t>REYNA ARISBETH</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>DORA LUZ</t>
+  </si>
+  <si>
+    <t>CRISTAL YOSELIN</t>
+  </si>
+  <si>
+    <t>EVELYN JOHANA</t>
+  </si>
+  <si>
+    <t>MARYFER</t>
+  </si>
+  <si>
+    <t>BERENICE</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>REGINA ISABEL</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>DIANA IVONNE</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>FATIMA MARILYN</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>ITZEL ABIGAIL</t>
+  </si>
+  <si>
+    <t>JAIME</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>LUIS REY</t>
+  </si>
+  <si>
+    <t>KIMBERLY</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>GABRIELA</t>
+  </si>
+  <si>
+    <t>FLOR GUADALUPE</t>
+  </si>
+  <si>
     <t>CARLOS FERNANDO</t>
-  </si>
-  <si>
-    <t>DORA LUZ</t>
   </si>
 </sst>
 </file>
@@ -1040,7 +1223,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1072,22 +1255,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920121</v>
+        <v>20330051920378</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1095,7 +1278,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920141</v>
+        <v>21330051920076</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
@@ -1104,13 +1287,13 @@
         <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1118,22 +1301,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>18330051920077</v>
+        <v>20330051920302</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1141,25 +1324,600 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920335</v>
+        <v>21330051920100</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920121</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920141</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920190</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920192</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920335</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920074</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920075</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920108</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920079</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920080</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21330051920083</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>21330051920084</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>21330051920085</v>
+      </c>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>21330051920086</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>21330051920089</v>
+      </c>
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" t="s">
+        <v>85</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>21330051920092</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>21330051920093</v>
+      </c>
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" t="s">
+        <v>87</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>21330051920096</v>
+      </c>
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" t="s">
+        <v>88</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>21330051920097</v>
+      </c>
+      <c r="B24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" t="s">
+        <v>89</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>21330051920099</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>21330051920383</v>
+      </c>
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>21330051920102</v>
+      </c>
+      <c r="B27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" t="s">
+        <v>92</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>21330051920104</v>
+      </c>
+      <c r="B28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" t="s">
+        <v>93</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>21330051920387</v>
+      </c>
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" t="s">
+        <v>94</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>18330051920077</v>
+      </c>
+      <c r="B30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" t="s">
+        <v>95</v>
+      </c>
+      <c r="E30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20222.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="69">
   <si>
     <t>Mat</t>
   </si>
@@ -91,144 +91,96 @@
     <t>CRUZ</t>
   </si>
   <si>
-    <t>FLORES</t>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ASCENCION</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ASCENCION</t>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
   </si>
   <si>
     <t>BALTAZARES</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>ELPIDIO</t>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>TZIZIHUA</t>
   </si>
   <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
   </si>
   <si>
     <t>CONTRERAS</t>
   </si>
   <si>
-    <t>TZIZIHUA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>QUIÑONES</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
     <t>REYLI</t>
   </si>
   <si>
-    <t>YARED</t>
-  </si>
-  <si>
-    <t>JOSE ISAAC</t>
-  </si>
-  <si>
     <t>ALONDRA YURIDIA</t>
   </si>
   <si>
@@ -241,70 +193,37 @@
     <t>REYNA ARISBETH</t>
   </si>
   <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
+    <t>DORA LUZ</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>KIMBERLY</t>
+  </si>
+  <si>
+    <t>CARLOS FERNANDO</t>
+  </si>
+  <si>
+    <t>ALAN URIEL</t>
+  </si>
+  <si>
     <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>DORA LUZ</t>
-  </si>
-  <si>
-    <t>CRISTAL YOSELIN</t>
-  </si>
-  <si>
-    <t>EVELYN JOHANA</t>
-  </si>
-  <si>
-    <t>MARYFER</t>
-  </si>
-  <si>
-    <t>BERENICE</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>REGINA ISABEL</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>DIANA IVONNE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>FATIMA MARILYN</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>ITZEL ABIGAIL</t>
-  </si>
-  <si>
-    <t>JAIME</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>LUIS REY</t>
-  </si>
-  <si>
-    <t>KIMBERLY</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>FLOR GUADALUPE</t>
-  </si>
-  <si>
-    <t>CARLOS FERNANDO</t>
   </si>
 </sst>
 </file>
@@ -705,16 +624,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>60.61</v>
+      </c>
+      <c r="H2">
+        <v>5.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -900,7 +822,7 @@
         <v>33</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1074,16 +996,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>60.61</v>
+      </c>
+      <c r="H2">
+        <v>5.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1223,7 +1148,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1261,10 +1186,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1278,16 +1203,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920076</v>
+        <v>21330051920100</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1301,22 +1226,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920302</v>
+        <v>21330051920121</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1324,22 +1249,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920100</v>
+        <v>21330051920141</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1347,7 +1272,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920121</v>
+        <v>20330051920190</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
@@ -1356,13 +1281,13 @@
         <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1370,22 +1295,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920141</v>
+        <v>20330051920214</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1393,22 +1318,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920190</v>
+        <v>20330051920335</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1416,62 +1341,62 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920192</v>
+        <v>21330051920080</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920335</v>
+        <v>21330051920084</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920074</v>
+        <v>21330051920086</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1485,16 +1410,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920075</v>
+        <v>21330051920092</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1508,16 +1433,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920108</v>
+        <v>21330051920097</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1531,16 +1456,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920079</v>
+        <v>21330051920383</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1554,22 +1479,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920080</v>
+        <v>18330051920077</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1577,22 +1502,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920083</v>
+        <v>20330051920061</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1600,323 +1525,24 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920084</v>
+        <v>20330051920192</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920085</v>
-      </c>
-      <c r="B18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" t="s">
-        <v>83</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920086</v>
-      </c>
-      <c r="B19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" t="s">
-        <v>84</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920089</v>
-      </c>
-      <c r="B20" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" t="s">
-        <v>85</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920092</v>
-      </c>
-      <c r="B21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" t="s">
-        <v>62</v>
-      </c>
-      <c r="D21" t="s">
-        <v>86</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920093</v>
-      </c>
-      <c r="B22" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" t="s">
-        <v>26</v>
-      </c>
-      <c r="D22" t="s">
-        <v>87</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920096</v>
-      </c>
-      <c r="B23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" t="s">
-        <v>63</v>
-      </c>
-      <c r="D23" t="s">
-        <v>88</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920097</v>
-      </c>
-      <c r="B24" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" t="s">
-        <v>64</v>
-      </c>
-      <c r="D24" t="s">
-        <v>89</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>11</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920099</v>
-      </c>
-      <c r="B25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" t="s">
-        <v>90</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>11</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920383</v>
-      </c>
-      <c r="B26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" t="s">
-        <v>91</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>11</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051920102</v>
-      </c>
-      <c r="B27" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" t="s">
-        <v>23</v>
-      </c>
-      <c r="D27" t="s">
-        <v>92</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>11</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>21330051920104</v>
-      </c>
-      <c r="B28" t="s">
-        <v>45</v>
-      </c>
-      <c r="C28" t="s">
-        <v>65</v>
-      </c>
-      <c r="D28" t="s">
-        <v>93</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>11</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>21330051920387</v>
-      </c>
-      <c r="B29" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" t="s">
-        <v>66</v>
-      </c>
-      <c r="D29" t="s">
-        <v>94</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>18330051920077</v>
-      </c>
-      <c r="B30" t="s">
-        <v>47</v>
-      </c>
-      <c r="C30" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" t="s">
-        <v>95</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>14</v>
-      </c>
-      <c r="G30">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20222.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="71">
   <si>
     <t>Mat</t>
   </si>
@@ -94,36 +94,39 @@
     <t>ROJAS</t>
   </si>
   <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ASCENCION</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ASCENCION</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
     <t>RICO</t>
   </si>
   <si>
@@ -139,36 +142,36 @@
     <t>MORENO</t>
   </si>
   <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>TZIZIHUA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>TZIZIHUA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -184,37 +187,40 @@
     <t>ALONDRA YURIDIA</t>
   </si>
   <si>
+    <t>KAREN ITZEL</t>
+  </si>
+  <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>REYNA ARISBETH</t>
+  </si>
+  <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
+    <t>DORA LUZ</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>KIMBERLY</t>
+  </si>
+  <si>
     <t>CRISTIAN FERMIN</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>REYNA ARISBETH</t>
-  </si>
-  <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>DORA LUZ</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>KIMBERLY</t>
   </si>
   <si>
     <t>CARLOS FERNANDO</t>
@@ -1148,7 +1154,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1186,10 +1192,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1209,10 +1215,10 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1226,16 +1232,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920121</v>
+        <v>21330051920111</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1258,7 +1264,7 @@
         <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1281,7 +1287,7 @@
         <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -1304,7 +1310,7 @@
         <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -1327,7 +1333,7 @@
         <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1350,7 +1356,7 @@
         <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1373,7 +1379,7 @@
         <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1396,7 +1402,7 @@
         <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1419,7 +1425,7 @@
         <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1442,7 +1448,7 @@
         <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1465,7 +1471,7 @@
         <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1479,7 +1485,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>18330051920077</v>
+        <v>21330051920121</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
@@ -1488,13 +1494,13 @@
         <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1502,7 +1508,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920061</v>
+        <v>18330051920077</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
@@ -1511,7 +1517,7 @@
         <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -1525,7 +1531,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920192</v>
+        <v>20330051920061</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
@@ -1534,15 +1540,38 @@
         <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>20330051920192</v>
+      </c>
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" t="s">
         <v>10</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F18" t="s">
         <v>15</v>
       </c>
-      <c r="G17">
+      <c r="G18">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20222.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20222.xlsx
@@ -627,10 +627,10 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>13</v>
@@ -639,7 +639,7 @@
         <v>20</v>
       </c>
       <c r="G2">
-        <v>60.61</v>
+        <v>58.82</v>
       </c>
       <c r="H2">
         <v>5.9</v>
@@ -822,10 +822,10 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2">
         <v>33</v>
@@ -999,10 +999,10 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>13</v>
@@ -1011,7 +1011,7 @@
         <v>20</v>
       </c>
       <c r="G2">
-        <v>60.61</v>
+        <v>58.82</v>
       </c>
       <c r="H2">
         <v>5.9</v>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20222.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="89">
   <si>
     <t>Mat</t>
   </si>
@@ -88,148 +88,202 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ASCENCION</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ASCENCION</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
     <t>RUGERIO</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
     <t>BALTAZARES</t>
   </si>
   <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>LEÓN</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>TZIZIHUA</t>
+  </si>
+  <si>
     <t>MENDEZ</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
     <t>MORENO</t>
   </si>
   <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>TZIZIHUA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
+    <t>VILLA</t>
   </si>
   <si>
     <t>CONTRERAS</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>YARED</t>
+  </si>
+  <si>
+    <t>RUBI</t>
+  </si>
+  <si>
+    <t>KAREN ITZEL</t>
+  </si>
+  <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>GABRIEL JOSUE</t>
+  </si>
+  <si>
+    <t>ALAN URIEL</t>
+  </si>
+  <si>
+    <t>REYNA ARISBETH</t>
+  </si>
+  <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
+    <t>DORA LUZ</t>
+  </si>
+  <si>
     <t>REYLI</t>
   </si>
   <si>
+    <t>EVELYN JOHANA</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>REGINA ISABEL</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>DIANA IVONNE</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
     <t>ALONDRA YURIDIA</t>
   </si>
   <si>
-    <t>KAREN ITZEL</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>REYNA ARISBETH</t>
-  </si>
-  <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>DORA LUZ</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
     <t>KIMBERLY</t>
   </si>
   <si>
-    <t>CRISTIAN FERMIN</t>
-  </si>
-  <si>
-    <t>CARLOS FERNANDO</t>
-  </si>
-  <si>
-    <t>ALAN URIEL</t>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
   </si>
   <si>
     <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>MICHELLE ROBERTA</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
   </si>
 </sst>
 </file>
@@ -630,16 +684,16 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>13</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>58.82</v>
+        <v>61.76</v>
       </c>
       <c r="H2">
         <v>5.9</v>
@@ -825,16 +879,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>32.35</v>
+      </c>
+      <c r="H2">
+        <v>5.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -848,16 +905,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -871,16 +931,19 @@
         <v>14</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H4">
+        <v>7.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -894,16 +957,19 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>52.38</v>
+      </c>
+      <c r="H5">
+        <v>5.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -917,16 +983,19 @@
         <v>26</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>69.23</v>
+      </c>
+      <c r="H6">
+        <v>6.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -940,16 +1009,19 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>57.89</v>
+      </c>
+      <c r="H7">
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -1002,19 +1074,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>58.82</v>
+        <v>32.35</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1031,16 +1103,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>54.17</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1066,7 +1138,7 @@
         <v>85.70999999999999</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1083,13 +1155,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>47.62</v>
+        <v>52.38</v>
       </c>
       <c r="H5">
         <v>5.9</v>
@@ -1109,13 +1181,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G6">
-        <v>76.92</v>
+        <v>69.23</v>
       </c>
       <c r="H6">
         <v>6.4</v>
@@ -1135,16 +1207,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>78.95</v>
+        <v>57.89</v>
       </c>
       <c r="H7">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -1154,7 +1226,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1186,16 +1258,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920378</v>
+        <v>21330051920076</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1209,16 +1281,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920100</v>
+        <v>21330051920107</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1238,10 +1310,10 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1261,10 +1333,10 @@
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1278,22 +1350,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920190</v>
+        <v>20330051920087</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1301,22 +1373,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920214</v>
+        <v>20330051920061</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1324,22 +1396,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920335</v>
+        <v>20330051920190</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1347,62 +1419,62 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920080</v>
+        <v>20330051920214</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920084</v>
+        <v>20330051920335</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920086</v>
+        <v>20330051920378</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1416,16 +1488,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920092</v>
+        <v>21330051920075</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1439,16 +1511,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920097</v>
+        <v>21330051920080</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1462,16 +1534,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920383</v>
+        <v>21330051920083</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1485,22 +1557,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920121</v>
+        <v>21330051920084</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1508,22 +1580,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>18330051920077</v>
+        <v>21330051920085</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1531,22 +1603,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920061</v>
+        <v>21330051920086</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1554,24 +1626,231 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
+        <v>21330051920092</v>
+      </c>
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>21330051920097</v>
+      </c>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>21330051920100</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>21330051920383</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>21330051920102</v>
+      </c>
+      <c r="B22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>21330051920118</v>
+      </c>
+      <c r="B23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
         <v>20330051920192</v>
       </c>
-      <c r="B18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" t="s">
-        <v>70</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="B24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" t="s">
         <v>10</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F24" t="s">
         <v>15</v>
       </c>
-      <c r="G18">
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>20330051920396</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>20330051920331</v>
+      </c>
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" t="s">
+        <v>87</v>
+      </c>
+      <c r="E26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>20330051920333</v>
+      </c>
+      <c r="B27" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" t="s">
+        <v>88</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20222.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="81">
   <si>
     <t>Mat</t>
   </si>
@@ -88,57 +88,48 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ASCENCION</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ASCENCION</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>OLIVARES</t>
   </si>
   <si>
     <t>PELLICO</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
     <t>RUGERIO</t>
   </si>
   <si>
@@ -151,54 +142,48 @@
     <t>ROMERO</t>
   </si>
   <si>
-    <t>LEÓN</t>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>VILLA</t>
   </si>
   <si>
     <t>NAJERA</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>TZIZIHUA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
@@ -208,70 +193,61 @@
     <t>SOLIS</t>
   </si>
   <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>ALONDRA YURIDIA</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>GABRIEL JOSUE</t>
+  </si>
+  <si>
+    <t>ALAN URIEL</t>
+  </si>
+  <si>
+    <t>REYNA ARISBETH</t>
+  </si>
+  <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
+    <t>REYLI</t>
+  </si>
+  <si>
+    <t>EVELYN JOHANA</t>
+  </si>
+  <si>
     <t>YARED</t>
   </si>
   <si>
-    <t>RUBI</t>
-  </si>
-  <si>
-    <t>KAREN ITZEL</t>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>REGINA ISABEL</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>DIANA IVONNE</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>KIMBERLY</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
   </si>
   <si>
     <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>GABRIEL JOSUE</t>
-  </si>
-  <si>
-    <t>ALAN URIEL</t>
-  </si>
-  <si>
-    <t>REYNA ARISBETH</t>
-  </si>
-  <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>DORA LUZ</t>
-  </si>
-  <si>
-    <t>REYLI</t>
-  </si>
-  <si>
-    <t>EVELYN JOHANA</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>REGINA ISABEL</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>DIANA IVONNE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
-    <t>KIMBERLY</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
   </si>
   <si>
     <t>JOCELYN</t>
@@ -1226,7 +1202,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1258,16 +1234,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920076</v>
+        <v>21330051920086</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1281,16 +1257,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920107</v>
+        <v>21330051920100</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1304,22 +1280,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920111</v>
+        <v>21330051920102</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1327,22 +1303,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920141</v>
+        <v>20330051920087</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1350,16 +1326,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920087</v>
+        <v>20330051920061</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1373,22 +1349,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920061</v>
+        <v>20330051920190</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1396,16 +1372,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920190</v>
+        <v>20330051920214</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -1419,62 +1395,62 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920214</v>
+        <v>20330051920378</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920335</v>
+        <v>21330051920075</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920378</v>
+        <v>21330051920076</v>
       </c>
       <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
         <v>32</v>
       </c>
-      <c r="C11" t="s">
-        <v>50</v>
-      </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1488,16 +1464,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920075</v>
+        <v>21330051920080</v>
       </c>
       <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
         <v>33</v>
       </c>
-      <c r="C12" t="s">
-        <v>51</v>
-      </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1511,16 +1487,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920080</v>
+        <v>21330051920083</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1534,16 +1510,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920083</v>
+        <v>21330051920084</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1557,16 +1533,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920084</v>
+        <v>21330051920085</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1580,16 +1556,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920085</v>
+        <v>21330051920092</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1603,16 +1579,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920086</v>
+        <v>21330051920097</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1626,16 +1602,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920092</v>
+        <v>21330051920383</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1649,22 +1625,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920097</v>
+        <v>21330051920118</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1672,22 +1648,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920100</v>
+        <v>21330051920141</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1695,22 +1671,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920383</v>
+        <v>20330051920192</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1718,22 +1694,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920102</v>
+        <v>20330051920396</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="D22" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1741,22 +1717,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920118</v>
+        <v>20330051920331</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D23" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1764,93 +1740,24 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920192</v>
+        <v>20330051920333</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D24" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E24" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>20330051920396</v>
-      </c>
-      <c r="B25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" t="s">
-        <v>61</v>
-      </c>
-      <c r="D25" t="s">
-        <v>86</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>16</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>20330051920331</v>
-      </c>
-      <c r="B26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" t="s">
-        <v>47</v>
-      </c>
-      <c r="D26" t="s">
-        <v>87</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>20330051920333</v>
-      </c>
-      <c r="B27" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" t="s">
-        <v>88</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>16</v>
-      </c>
-      <c r="G27">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20222.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="83">
   <si>
     <t>Mat</t>
   </si>
@@ -94,6 +94,9 @@
     <t>ROJAS</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -139,15 +142,15 @@
     <t>MUÑOZ</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>RIVERA</t>
   </si>
   <si>
     <t>MORENO</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
@@ -197,6 +200,9 @@
   </si>
   <si>
     <t>ALONDRA YURIDIA</t>
+  </si>
+  <si>
+    <t>CITLALI ESPERANZA</t>
   </si>
   <si>
     <t>ANGEL DAVID</t>
@@ -1202,7 +1208,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1243,7 +1249,7 @@
         <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1266,7 +1272,7 @@
         <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1280,16 +1286,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920102</v>
+        <v>21330051920101</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1303,22 +1309,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920087</v>
+        <v>21330051920102</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1326,16 +1332,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920061</v>
+        <v>20330051920087</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1349,7 +1355,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920190</v>
+        <v>20330051920061</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
@@ -1358,13 +1364,13 @@
         <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1372,16 +1378,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920214</v>
+        <v>20330051920190</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
         <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -1395,30 +1401,30 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920378</v>
+        <v>20330051920214</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920075</v>
+        <v>20330051920378</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
@@ -1427,7 +1433,7 @@
         <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1441,16 +1447,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920076</v>
+        <v>21330051920075</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1464,7 +1470,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920080</v>
+        <v>21330051920076</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
@@ -1473,7 +1479,7 @@
         <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1487,16 +1493,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920083</v>
+        <v>21330051920080</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1510,7 +1516,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920084</v>
+        <v>21330051920083</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
@@ -1519,7 +1525,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1533,16 +1539,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920085</v>
+        <v>21330051920084</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
         <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1556,16 +1562,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920092</v>
+        <v>21330051920085</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
         <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1579,7 +1585,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920097</v>
+        <v>21330051920092</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
@@ -1588,7 +1594,7 @@
         <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1602,16 +1608,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920383</v>
+        <v>21330051920097</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1625,22 +1631,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920118</v>
+        <v>21330051920383</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="D19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1648,7 +1654,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920141</v>
+        <v>21330051920118</v>
       </c>
       <c r="B20" t="s">
         <v>32</v>
@@ -1657,13 +1663,13 @@
         <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1671,22 +1677,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920192</v>
+        <v>21330051920141</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C21" t="s">
         <v>55</v>
       </c>
       <c r="D21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1694,7 +1700,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920396</v>
+        <v>20330051920192</v>
       </c>
       <c r="B22" t="s">
         <v>39</v>
@@ -1703,13 +1709,13 @@
         <v>56</v>
       </c>
       <c r="D22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1717,16 +1723,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920331</v>
+        <v>20330051920396</v>
       </c>
       <c r="B23" t="s">
         <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="D23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -1740,16 +1746,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920333</v>
+        <v>20330051920331</v>
       </c>
       <c r="B24" t="s">
         <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
@@ -1758,6 +1764,29 @@
         <v>16</v>
       </c>
       <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>20330051920333</v>
+      </c>
+      <c r="B25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20222.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="85">
   <si>
     <t>Mat</t>
   </si>
@@ -100,6 +100,9 @@
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
     <t>MARROQUIN</t>
   </si>
   <si>
@@ -206,6 +209,9 @@
   </si>
   <si>
     <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
   </si>
   <si>
     <t>GABRIEL JOSUE</t>
@@ -1208,7 +1214,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1246,10 +1252,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1269,10 +1275,10 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1292,10 +1298,10 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1315,10 +1321,10 @@
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1332,22 +1338,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920087</v>
+        <v>21330051920103</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1355,16 +1361,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920061</v>
+        <v>20330051920087</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1378,7 +1384,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920190</v>
+        <v>20330051920061</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
@@ -1387,13 +1393,13 @@
         <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1401,16 +1407,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920214</v>
+        <v>20330051920190</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -1424,30 +1430,30 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920378</v>
+        <v>20330051920214</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
         <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920075</v>
+        <v>20330051920378</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
@@ -1456,7 +1462,7 @@
         <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1470,16 +1476,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920076</v>
+        <v>21330051920075</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1493,7 +1499,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920080</v>
+        <v>21330051920076</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
@@ -1502,7 +1508,7 @@
         <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1516,16 +1522,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920083</v>
+        <v>21330051920080</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1539,7 +1545,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920084</v>
+        <v>21330051920083</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
@@ -1548,7 +1554,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1562,16 +1568,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920085</v>
+        <v>21330051920084</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
         <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1585,16 +1591,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920092</v>
+        <v>21330051920085</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
         <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1608,7 +1614,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920097</v>
+        <v>21330051920092</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
@@ -1617,7 +1623,7 @@
         <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1631,16 +1637,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920383</v>
+        <v>21330051920097</v>
       </c>
       <c r="B19" t="s">
         <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1654,22 +1660,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920118</v>
+        <v>21330051920383</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="D20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1677,7 +1683,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920141</v>
+        <v>21330051920118</v>
       </c>
       <c r="B21" t="s">
         <v>33</v>
@@ -1686,13 +1692,13 @@
         <v>55</v>
       </c>
       <c r="D21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1700,22 +1706,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920192</v>
+        <v>21330051920141</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
         <v>56</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1723,7 +1729,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920396</v>
+        <v>20330051920192</v>
       </c>
       <c r="B23" t="s">
         <v>40</v>
@@ -1732,13 +1738,13 @@
         <v>57</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1746,16 +1752,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920331</v>
+        <v>20330051920396</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
@@ -1769,16 +1775,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920333</v>
+        <v>20330051920331</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
@@ -1787,6 +1793,29 @@
         <v>16</v>
       </c>
       <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>20330051920333</v>
+      </c>
+      <c r="B26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" t="s">
+        <v>84</v>
+      </c>
+      <c r="E26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20222.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20222.xlsx
@@ -94,48 +94,48 @@
     <t>ROJAS</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ASCENCION</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ASCENCION</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
     <t>RUGERIO</t>
   </si>
   <si>
@@ -151,39 +151,39 @@
     <t>MORENO</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
     <t>VILLA</t>
   </si>
   <si>
@@ -205,52 +205,52 @@
     <t>ALONDRA YURIDIA</t>
   </si>
   <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
+  </si>
+  <si>
+    <t>GABRIEL JOSUE</t>
+  </si>
+  <si>
+    <t>ALAN URIEL</t>
+  </si>
+  <si>
+    <t>REYNA ARISBETH</t>
+  </si>
+  <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
+    <t>REYLI</t>
+  </si>
+  <si>
+    <t>EVELYN JOHANA</t>
+  </si>
+  <si>
+    <t>YARED</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>REGINA ISABEL</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>DIANA IVONNE</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
     <t>CITLALI ESPERANZA</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>ALMA KAREN</t>
-  </si>
-  <si>
-    <t>GABRIEL JOSUE</t>
-  </si>
-  <si>
-    <t>ALAN URIEL</t>
-  </si>
-  <si>
-    <t>REYNA ARISBETH</t>
-  </si>
-  <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>REYLI</t>
-  </si>
-  <si>
-    <t>EVELYN JOHANA</t>
-  </si>
-  <si>
-    <t>YARED</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>REGINA ISABEL</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>DIANA IVONNE</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
   </si>
   <si>
     <t>KIMBERLY</t>
@@ -1292,13 +1292,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920101</v>
+        <v>21330051920102</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
         <v>62</v>
@@ -1315,13 +1315,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920102</v>
+        <v>21330051920103</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
         <v>63</v>
@@ -1338,22 +1338,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920103</v>
+        <v>20330051920087</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
         <v>64</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1361,13 +1361,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920087</v>
+        <v>20330051920061</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
         <v>65</v>
@@ -1384,7 +1384,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920061</v>
+        <v>20330051920190</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
@@ -1396,10 +1396,10 @@
         <v>66</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920190</v>
+        <v>20330051920214</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920214</v>
+        <v>20330051920378</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
         <v>47</v>
@@ -1442,18 +1442,18 @@
         <v>68</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920378</v>
+        <v>21330051920075</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
@@ -1476,13 +1476,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920075</v>
+        <v>21330051920076</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
         <v>70</v>
@@ -1499,7 +1499,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920076</v>
+        <v>21330051920080</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
@@ -1522,13 +1522,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920080</v>
+        <v>21330051920083</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
         <v>72</v>
@@ -1545,7 +1545,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920083</v>
+        <v>21330051920084</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920084</v>
+        <v>21330051920085</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
         <v>51</v>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920085</v>
+        <v>21330051920092</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
         <v>52</v>
@@ -1614,7 +1614,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920092</v>
+        <v>21330051920097</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
@@ -1637,7 +1637,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920097</v>
+        <v>21330051920101</v>
       </c>
       <c r="B19" t="s">
         <v>38</v>
@@ -1666,7 +1666,7 @@
         <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D20" t="s">
         <v>78</v>
@@ -1686,7 +1686,7 @@
         <v>21330051920118</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C21" t="s">
         <v>55</v>
@@ -1709,7 +1709,7 @@
         <v>21330051920141</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C22" t="s">
         <v>56</v>
@@ -1778,10 +1778,10 @@
         <v>20330051920331</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D25" t="s">
         <v>83</v>
@@ -1801,7 +1801,7 @@
         <v>20330051920333</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C26" t="s">
         <v>59</v>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20222.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="68">
   <si>
     <t>Mat</t>
   </si>
@@ -88,70 +88,82 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ASCENCION</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>LEÓN</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
   </si>
   <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
+    <t>HIPOLITO</t>
   </si>
   <si>
     <t>MORENO</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>LEON</t>
   </si>
   <si>
     <t>CASTILLO</t>
@@ -160,118 +172,55 @@
     <t>HUERTA</t>
   </si>
   <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
+    <t>MIROSLAVA</t>
   </si>
   <si>
     <t>FATIMA</t>
   </si>
   <si>
+    <t>ALMA KAREN</t>
+  </si>
+  <si>
+    <t>RUBI</t>
+  </si>
+  <si>
+    <t>ALDIR ADALBERTO</t>
+  </si>
+  <si>
+    <t>JESUS URIEL</t>
+  </si>
+  <si>
+    <t>REYLI</t>
+  </si>
+  <si>
+    <t>EVELYN JOHANA</t>
+  </si>
+  <si>
+    <t>YARED</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
     <t>ALONDRA YURIDIA</t>
   </si>
   <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>ALMA KAREN</t>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
   </si>
   <si>
     <t>GABRIEL JOSUE</t>
   </si>
   <si>
-    <t>ALAN URIEL</t>
-  </si>
-  <si>
-    <t>REYNA ARISBETH</t>
+    <t>JULIO CESAR</t>
   </si>
   <si>
     <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>REYLI</t>
-  </si>
-  <si>
-    <t>EVELYN JOHANA</t>
-  </si>
-  <si>
-    <t>YARED</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>REGINA ISABEL</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>DIANA IVONNE</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>CITLALI ESPERANZA</t>
-  </si>
-  <si>
-    <t>KIMBERLY</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>MICHELLE ROBERTA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
   </si>
 </sst>
 </file>
@@ -1065,16 +1014,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>32.35</v>
+        <v>58.82</v>
       </c>
       <c r="H2">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1091,13 +1040,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>54.17</v>
       </c>
       <c r="H3">
         <v>6.1</v>
@@ -1143,16 +1092,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>52.38</v>
+        <v>61.9</v>
       </c>
       <c r="H5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1169,16 +1118,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>69.23</v>
+        <v>84.62</v>
       </c>
       <c r="H6">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1195,16 +1144,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G7">
-        <v>57.89</v>
+        <v>89.47</v>
       </c>
       <c r="H7">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -1214,7 +1163,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1246,16 +1195,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920086</v>
+        <v>21330051920078</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1269,16 +1218,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920100</v>
+        <v>21330051920086</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1292,16 +1241,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920102</v>
+        <v>21330051920103</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1315,16 +1264,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920103</v>
+        <v>21330051920107</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1338,16 +1287,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920087</v>
+        <v>20330051920065</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1361,22 +1310,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920061</v>
+        <v>20330051920259</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1384,62 +1333,62 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920190</v>
+        <v>20330051920378</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920214</v>
+        <v>21330051920075</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920378</v>
+        <v>21330051920076</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1453,16 +1402,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920075</v>
+        <v>21330051920080</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1476,16 +1425,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920076</v>
+        <v>21330051920092</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1499,16 +1448,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920080</v>
+        <v>21330051920100</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1522,22 +1471,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920083</v>
+        <v>21330051920141</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1545,22 +1494,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920084</v>
+        <v>20330051920080</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1568,22 +1517,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920085</v>
+        <v>20330051920087</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1591,22 +1540,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920092</v>
+        <v>20330051920210</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1614,208 +1563,24 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920097</v>
+        <v>20330051920214</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920101</v>
-      </c>
-      <c r="B19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" t="s">
-        <v>77</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920383</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" t="s">
-        <v>78</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920118</v>
-      </c>
-      <c r="B21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21" t="s">
-        <v>79</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920141</v>
-      </c>
-      <c r="B22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22" t="s">
-        <v>80</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920192</v>
-      </c>
-      <c r="B23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" t="s">
-        <v>57</v>
-      </c>
-      <c r="D23" t="s">
-        <v>81</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920396</v>
-      </c>
-      <c r="B24" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" t="s">
-        <v>58</v>
-      </c>
-      <c r="D24" t="s">
-        <v>82</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>16</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>20330051920331</v>
-      </c>
-      <c r="B25" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" t="s">
-        <v>83</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>16</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>20330051920333</v>
-      </c>
-      <c r="B26" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26" t="s">
-        <v>59</v>
-      </c>
-      <c r="D26" t="s">
-        <v>84</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G26">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20222.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="79">
   <si>
     <t>Mat</t>
   </si>
@@ -100,36 +100,48 @@
     <t>TENTZOHUA</t>
   </si>
   <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>CANUTO</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
     <t>SARMIENTO</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
     <t>ROBLES</t>
   </si>
   <si>
@@ -142,30 +154,39 @@
     <t>LEÓN</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>CAPORAL</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
     <t>URBINA</t>
   </si>
   <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
     <t>CASTILLO</t>
   </si>
   <si>
@@ -184,37 +205,49 @@
     <t>RUBI</t>
   </si>
   <si>
+    <t>KAREN ITZEL</t>
+  </si>
+  <si>
+    <t>LOGAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>JESUS URIEL</t>
+  </si>
+  <si>
+    <t>REYLI</t>
+  </si>
+  <si>
+    <t>EVELYN JOHANA</t>
+  </si>
+  <si>
+    <t>YARED</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>ALONDRA YURIDIA</t>
+  </si>
+  <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>GABRIEL JOSUE</t>
+  </si>
+  <si>
     <t>ALDIR ADALBERTO</t>
-  </si>
-  <si>
-    <t>JESUS URIEL</t>
-  </si>
-  <si>
-    <t>REYLI</t>
-  </si>
-  <si>
-    <t>EVELYN JOHANA</t>
-  </si>
-  <si>
-    <t>YARED</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>GABRIEL JOSUE</t>
   </si>
   <si>
     <t>JULIO CESAR</t>
@@ -1163,7 +1196,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1201,10 +1234,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1224,10 +1257,10 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1250,7 +1283,7 @@
         <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1270,10 +1303,10 @@
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1287,22 +1320,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920065</v>
+        <v>21330051920111</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1310,22 +1343,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920259</v>
+        <v>21330051920391</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1333,85 +1366,85 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920378</v>
+        <v>20330051920071</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920075</v>
+        <v>20330051920073</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920076</v>
+        <v>20330051920259</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920080</v>
+        <v>20330051920378</v>
       </c>
       <c r="B11" t="s">
         <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1425,16 +1458,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920092</v>
+        <v>21330051920075</v>
       </c>
       <c r="B12" t="s">
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1448,16 +1481,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920100</v>
+        <v>21330051920076</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1471,22 +1504,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920141</v>
+        <v>21330051920080</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1494,22 +1527,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920080</v>
+        <v>21330051920092</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1517,22 +1550,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920087</v>
+        <v>21330051920100</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1540,22 +1573,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920210</v>
+        <v>21330051920141</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1563,24 +1596,116 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920214</v>
+        <v>20330051920080</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>20330051920087</v>
+      </c>
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>20330051920065</v>
+      </c>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>20330051920210</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" t="s">
         <v>10</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F21" t="s">
         <v>15</v>
       </c>
-      <c r="G18">
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>20330051920214</v>
+      </c>
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20222.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="80">
   <si>
     <t>Mat</t>
   </si>
@@ -209,6 +209,9 @@
   </si>
   <si>
     <t>LOGAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
   </si>
   <si>
     <t>MARCO ANTONIO</t>
@@ -1196,7 +1199,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1366,10 +1369,10 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920071</v>
+        <v>21330051920125</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
         <v>34</v>
@@ -1378,10 +1381,10 @@
         <v>64</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1389,13 +1392,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920073</v>
+        <v>20330051920071</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
         <v>65</v>
@@ -1412,22 +1415,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920259</v>
+        <v>20330051920073</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
         <v>66</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1435,36 +1438,36 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920378</v>
+        <v>20330051920259</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
         <v>67</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920075</v>
+        <v>20330051920378</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
         <v>68</v>
@@ -1481,13 +1484,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920076</v>
+        <v>21330051920075</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
         <v>69</v>
@@ -1504,13 +1507,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920080</v>
+        <v>21330051920076</v>
       </c>
       <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
         <v>35</v>
-      </c>
-      <c r="C14" t="s">
-        <v>50</v>
       </c>
       <c r="D14" t="s">
         <v>70</v>
@@ -1527,13 +1530,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920092</v>
+        <v>21330051920080</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
         <v>71</v>
@@ -1550,13 +1553,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920100</v>
+        <v>21330051920092</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
         <v>72</v>
@@ -1573,13 +1576,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920141</v>
+        <v>21330051920100</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
         <v>73</v>
@@ -1588,7 +1591,7 @@
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1596,22 +1599,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920080</v>
+        <v>21330051920141</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
         <v>74</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1619,13 +1622,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920087</v>
+        <v>20330051920080</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
         <v>75</v>
@@ -1642,13 +1645,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920065</v>
+        <v>20330051920087</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="D20" t="s">
         <v>76</v>
@@ -1665,22 +1668,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920210</v>
+        <v>20330051920065</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
         <v>77</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1688,13 +1691,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920214</v>
+        <v>20330051920210</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D22" t="s">
         <v>78</v>
@@ -1706,6 +1709,29 @@
         <v>15</v>
       </c>
       <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>20330051920214</v>
+      </c>
+      <c r="B23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" t="s">
+        <v>79</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23">
         <v>1</v>
       </c>
     </row>
